--- a/backend/real_data/classes_information_3.xlsx
+++ b/backend/real_data/classes_information_3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\school_timeTable_v1.9\backend\real_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\school_timeTable_v2.0\backend\real_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC5EB30-D480-48B0-8778-E375836E4FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68090439-2B2B-4F93-B01D-C5679800870B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="55">
   <si>
     <t>10A1</t>
   </si>
@@ -163,39 +163,6 @@
     <t>TO12, NV12, TA12, LS12, GDTC12, QP12, GDĐP12, HĐTN12, ĐL12, GDKT12,CNCN12, VL12</t>
   </si>
   <si>
-    <t>TO12, NV12, TA12, LS12, GDTC12, QP12, GDĐP12, HĐTN13, ĐL12, GDKT12,CNCN12, VL12</t>
-  </si>
-  <si>
-    <t>TO12, NV12, TA12, LS12, GDTC12, QP12, GDĐP12, HĐTN14, ĐL12, GDKT12,CNCN12, VL12</t>
-  </si>
-  <si>
-    <t>TO12, NV12, TA12, LS12, GDTC12, QP12, GDĐP12, HĐTN15, ĐL12, GDKT12,TH12, VL12</t>
-  </si>
-  <si>
-    <t>TO12, NV12, TA12, LS12, GDTC12, QP12, GDĐP12, HĐTN16, ĐL12, GDKT12,TH12, VL12</t>
-  </si>
-  <si>
-    <t>TO12, NV12, TA12, LS12, GDTC12, QP12, GDĐP12, HĐTN17, ĐL12, GDKT12,TH12, VL12</t>
-  </si>
-  <si>
-    <t>TO12, NV12, TA12, LS12, GDTC12, QP12, GDĐP12, HĐTN18, VL12, HO12, SH12, CNCN12</t>
-  </si>
-  <si>
-    <t>TO12, NV12, TA12, LS12, GDTC12, QP12, GDĐP12, HĐTN19, VL12, HO12, SH12, TH12</t>
-  </si>
-  <si>
-    <t>TO12, NV12, TA12, LS12, GDTC12, QP12, GDĐP12, HĐTN20, VL12, HO12, SH12, TH12</t>
-  </si>
-  <si>
-    <t>TO12, NV12, TA12, LS12, GDTC12, QP12, GDĐP12, HĐTN21, VL12, HO12, SH12, TH12</t>
-  </si>
-  <si>
-    <t>TO12, NV12, TA12, LS12, GDTC12, QP12, GDĐP12, HĐTN22, VL12, HO12, SH12, TH12</t>
-  </si>
-  <si>
-    <t>TO12, NV12, TA12, LS12, GDTC12, QP12, GDĐP12, HĐTN23, VL12, HO12, SH12, TH12</t>
-  </si>
-  <si>
     <t>Lớp Chuyên Đề</t>
   </si>
   <si>
@@ -209,6 +176,15 @@
   </si>
   <si>
     <t>T-H-Sinh</t>
+  </si>
+  <si>
+    <t>TO12, NV12, TA12, LS12, GDTC12, QP12, GDĐP12, HĐTN12, ĐL12, GDKT12,TH12, VL12</t>
+  </si>
+  <si>
+    <t>TO12, NV12, TA12, LS12, GDTC12, QP12, GDĐP12, HĐTN12, VL12, HO12, SH12, CNCN12</t>
+  </si>
+  <si>
+    <t>TO12, NV12, TA12, LS12, GDTC12, QP12, GDĐP12, HĐTN12, VL12, HO12, SH12, TH12</t>
   </si>
 </sst>
 </file>
@@ -289,7 +265,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -611,7 +587,7 @@
         <v>37</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -622,7 +598,7 @@
         <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -633,7 +609,7 @@
         <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -644,7 +620,7 @@
         <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -655,7 +631,7 @@
         <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -666,7 +642,7 @@
         <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -677,7 +653,7 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -688,7 +664,7 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -699,7 +675,7 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -710,7 +686,7 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -721,7 +697,7 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -732,7 +708,7 @@
         <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -743,7 +719,7 @@
         <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -754,7 +730,7 @@
         <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -765,7 +741,7 @@
         <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -776,7 +752,7 @@
         <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -787,7 +763,7 @@
         <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -798,7 +774,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -809,7 +785,7 @@
         <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -820,7 +796,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -831,7 +807,7 @@
         <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -842,7 +818,7 @@
         <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -853,7 +829,7 @@
         <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -864,7 +840,7 @@
         <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -875,7 +851,7 @@
         <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -886,7 +862,7 @@
         <v>46</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -894,10 +870,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -905,10 +881,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -916,10 +892,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -927,10 +903,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -938,10 +914,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -949,10 +925,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -960,10 +936,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C33" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -974,7 +950,7 @@
         <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -982,10 +958,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -993,10 +969,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -1004,10 +980,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
